--- a/artfynd/A 11648-2021 artfynd.xlsx
+++ b/artfynd/A 11648-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11648-2021 artfynd.xlsx
+++ b/artfynd/A 11648-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>73982909</v>
       </c>
       <c r="B2" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499268.661141818</v>
+        <v>499269</v>
       </c>
       <c r="R2" t="n">
-        <v>6327252.756205679</v>
+        <v>6327253</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1979-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74907008</v>
       </c>
       <c r="B3" t="n">
-        <v>100146</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499268.661141818</v>
+        <v>499269</v>
       </c>
       <c r="R3" t="n">
-        <v>6327252.756205679</v>
+        <v>6327253</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1979-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 11648-2021 artfynd.xlsx
+++ b/artfynd/A 11648-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982909</v>
       </c>
       <c r="B2" t="n">
-        <v>107283</v>
+        <v>107292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74907008</v>
       </c>
       <c r="B3" t="n">
-        <v>102454</v>
+        <v>102460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2021 artfynd.xlsx
+++ b/artfynd/A 11648-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982909</v>
       </c>
       <c r="B2" t="n">
-        <v>107292</v>
+        <v>107297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74907008</v>
       </c>
       <c r="B3" t="n">
-        <v>102460</v>
+        <v>102461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2021 artfynd.xlsx
+++ b/artfynd/A 11648-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982909</v>
       </c>
       <c r="B2" t="n">
-        <v>107297</v>
+        <v>107325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74907008</v>
       </c>
       <c r="B3" t="n">
-        <v>102461</v>
+        <v>102488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2021 artfynd.xlsx
+++ b/artfynd/A 11648-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982909</v>
       </c>
       <c r="B2" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74907008</v>
       </c>
       <c r="B3" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2021 artfynd.xlsx
+++ b/artfynd/A 11648-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982909</v>
       </c>
       <c r="B2" t="n">
-        <v>107331</v>
+        <v>107338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74907008</v>
       </c>
       <c r="B3" t="n">
-        <v>102494</v>
+        <v>102501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2021 artfynd.xlsx
+++ b/artfynd/A 11648-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982909</v>
       </c>
       <c r="B2" t="n">
-        <v>107338</v>
+        <v>107342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74907008</v>
       </c>
       <c r="B3" t="n">
-        <v>102501</v>
+        <v>102505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2021 artfynd.xlsx
+++ b/artfynd/A 11648-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982909</v>
       </c>
       <c r="B2" t="n">
-        <v>107342</v>
+        <v>107350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74907008</v>
       </c>
       <c r="B3" t="n">
-        <v>102505</v>
+        <v>102512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2021 artfynd.xlsx
+++ b/artfynd/A 11648-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982909</v>
       </c>
       <c r="B2" t="n">
-        <v>107353</v>
+        <v>107358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74907008</v>
       </c>
       <c r="B3" t="n">
-        <v>102515</v>
+        <v>102520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2021 artfynd.xlsx
+++ b/artfynd/A 11648-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982909</v>
       </c>
       <c r="B2" t="n">
-        <v>107358</v>
+        <v>107366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74907008</v>
       </c>
       <c r="B3" t="n">
-        <v>102520</v>
+        <v>102528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2021 artfynd.xlsx
+++ b/artfynd/A 11648-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982909</v>
       </c>
       <c r="B2" t="n">
-        <v>107366</v>
+        <v>107376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74907008</v>
       </c>
       <c r="B3" t="n">
-        <v>102528</v>
+        <v>102538</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
